--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -1689,50 +1689,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126244721</v>
+        <v>126244493</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>100525</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604909</v>
+        <v>604804</v>
       </c>
       <c r="R12" t="n">
-        <v>6923259</v>
+        <v>6923297</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1765,11 +1760,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,45 +1786,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126244493</v>
+        <v>126244721</v>
       </c>
       <c r="B13" t="n">
-        <v>100525</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604804</v>
+        <v>604909</v>
       </c>
       <c r="R13" t="n">
-        <v>6923297</v>
+        <v>6923259</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,6 +1862,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B3" t="n">
-        <v>56847</v>
+        <v>57652</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,14 +810,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R3" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>56847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,10 +917,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R4" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243913</v>
+        <v>126244314</v>
       </c>
       <c r="B5" t="n">
-        <v>91236</v>
+        <v>91692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604846</v>
+        <v>604829</v>
       </c>
       <c r="R5" t="n">
-        <v>6923320</v>
+        <v>6923326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126244314</v>
+        <v>126243913</v>
       </c>
       <c r="B6" t="n">
-        <v>91690</v>
+        <v>91238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604829</v>
+        <v>604846</v>
       </c>
       <c r="R6" t="n">
-        <v>6923326</v>
+        <v>6923320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1197,7 @@
         <v>126243134</v>
       </c>
       <c r="B7" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>126242980</v>
       </c>
       <c r="B8" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242691</v>
+        <v>126244102</v>
       </c>
       <c r="B9" t="n">
-        <v>57652</v>
+        <v>91534</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,39 +1399,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604953</v>
+        <v>604829</v>
       </c>
       <c r="R9" t="n">
-        <v>6923370</v>
+        <v>6923326</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244102</v>
+        <v>126241081</v>
       </c>
       <c r="B10" t="n">
-        <v>91532</v>
+        <v>91238</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604829</v>
+        <v>604931</v>
       </c>
       <c r="R10" t="n">
-        <v>6923326</v>
+        <v>6923243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126241081</v>
+        <v>126242691</v>
       </c>
       <c r="B11" t="n">
-        <v>91236</v>
+        <v>57652</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,34 +1593,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604931</v>
+        <v>604953</v>
       </c>
       <c r="R11" t="n">
-        <v>6923243</v>
+        <v>6923370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1689,45 +1689,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126244493</v>
+        <v>126244721</v>
       </c>
       <c r="B12" t="n">
-        <v>100525</v>
+        <v>57652</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>604804</v>
+        <v>604909</v>
       </c>
       <c r="R12" t="n">
-        <v>6923297</v>
+        <v>6923259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1760,6 +1765,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1786,50 +1796,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126244721</v>
+        <v>126244493</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>100527</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604909</v>
+        <v>604804</v>
       </c>
       <c r="R13" t="n">
-        <v>6923259</v>
+        <v>6923297</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1862,11 +1867,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1893,45 +1893,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126242864</v>
+        <v>126242541</v>
       </c>
       <c r="B14" t="n">
-        <v>97221</v>
+        <v>57652</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604927</v>
+        <v>604966</v>
       </c>
       <c r="R14" t="n">
-        <v>6923374</v>
+        <v>6923343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,6 +1969,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1990,50 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126242541</v>
+        <v>126242864</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>97223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604966</v>
+        <v>604927</v>
       </c>
       <c r="R15" t="n">
-        <v>6923343</v>
+        <v>6923374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2071,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>126243475</v>
       </c>
       <c r="B16" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>126243781</v>
       </c>
       <c r="B17" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126241171</v>
       </c>
       <c r="B18" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>126241533</v>
       </c>
       <c r="B20" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126242587</v>
+        <v>126242839</v>
       </c>
       <c r="B21" t="n">
-        <v>91236</v>
+        <v>91692</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>604966</v>
+        <v>604916</v>
       </c>
       <c r="R21" t="n">
-        <v>6923343</v>
+        <v>6923365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126242839</v>
+        <v>126242587</v>
       </c>
       <c r="B22" t="n">
-        <v>91690</v>
+        <v>91238</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>604916</v>
+        <v>604966</v>
       </c>
       <c r="R22" t="n">
-        <v>6923365</v>
+        <v>6923343</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126241499</v>
+        <v>126241476</v>
       </c>
       <c r="B23" t="n">
-        <v>57812</v>
+        <v>91238</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,43 +2797,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604927</v>
+        <v>604946</v>
       </c>
       <c r="R23" t="n">
-        <v>6923303</v>
+        <v>6923307</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,10 +2883,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126241476</v>
+        <v>126241499</v>
       </c>
       <c r="B24" t="n">
-        <v>91236</v>
+        <v>57812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2903,34 +2894,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604946</v>
+        <v>604927</v>
       </c>
       <c r="R24" t="n">
-        <v>6923307</v>
+        <v>6923303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3098,7 +3098,7 @@
         <v>126242636</v>
       </c>
       <c r="B26" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126244910</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B3" t="n">
-        <v>57652</v>
+        <v>56851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,10 +810,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R3" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +893,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B4" t="n">
-        <v>56847</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,14 +921,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R4" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126244314</v>
+        <v>126243913</v>
       </c>
       <c r="B5" t="n">
-        <v>91692</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604829</v>
+        <v>604846</v>
       </c>
       <c r="R5" t="n">
-        <v>6923326</v>
+        <v>6923320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243913</v>
+        <v>126244314</v>
       </c>
       <c r="B6" t="n">
-        <v>91238</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604846</v>
+        <v>604829</v>
       </c>
       <c r="R6" t="n">
-        <v>6923320</v>
+        <v>6923326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126243134</v>
+        <v>126242980</v>
       </c>
       <c r="B7" t="n">
-        <v>91534</v>
+        <v>91207</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604973</v>
+        <v>604937</v>
       </c>
       <c r="R7" t="n">
-        <v>6923382</v>
+        <v>6923369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126242980</v>
+        <v>126243134</v>
       </c>
       <c r="B8" t="n">
-        <v>91203</v>
+        <v>91538</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604937</v>
+        <v>604973</v>
       </c>
       <c r="R8" t="n">
-        <v>6923369</v>
+        <v>6923382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
         <v>126244102</v>
       </c>
       <c r="B9" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126241081</v>
+        <v>126242691</v>
       </c>
       <c r="B10" t="n">
-        <v>91238</v>
+        <v>57656</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,34 +1496,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604931</v>
+        <v>604953</v>
       </c>
       <c r="R10" t="n">
-        <v>6923243</v>
+        <v>6923370</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,6 +1561,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1582,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126242691</v>
+        <v>126241081</v>
       </c>
       <c r="B11" t="n">
-        <v>57652</v>
+        <v>91242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,39 +1603,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604953</v>
+        <v>604931</v>
       </c>
       <c r="R11" t="n">
-        <v>6923370</v>
+        <v>6923243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,7 +1692,7 @@
         <v>126244721</v>
       </c>
       <c r="B12" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126244493</v>
       </c>
       <c r="B13" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,50 +1893,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126242541</v>
+        <v>126242864</v>
       </c>
       <c r="B14" t="n">
-        <v>57652</v>
+        <v>97227</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604966</v>
+        <v>604927</v>
       </c>
       <c r="R14" t="n">
-        <v>6923343</v>
+        <v>6923374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,11 +1964,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,45 +1990,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126242864</v>
+        <v>126242541</v>
       </c>
       <c r="B15" t="n">
-        <v>97223</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604927</v>
+        <v>604966</v>
       </c>
       <c r="R15" t="n">
-        <v>6923374</v>
+        <v>6923343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,6 +2066,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2100,7 +2100,7 @@
         <v>126243475</v>
       </c>
       <c r="B16" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>126243781</v>
       </c>
       <c r="B17" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126241171</v>
       </c>
       <c r="B18" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126242290</v>
       </c>
       <c r="B19" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>126241533</v>
       </c>
       <c r="B20" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>126242839</v>
       </c>
       <c r="B21" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>126242587</v>
       </c>
       <c r="B22" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>126241476</v>
       </c>
       <c r="B23" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>126241499</v>
       </c>
       <c r="B24" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>126244626</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58025</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>126242636</v>
       </c>
       <c r="B26" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B3" t="n">
-        <v>56851</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,14 +810,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R3" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>56851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,10 +917,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R4" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1893,45 +1893,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126242864</v>
+        <v>126242541</v>
       </c>
       <c r="B14" t="n">
-        <v>97227</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604927</v>
+        <v>604966</v>
       </c>
       <c r="R14" t="n">
-        <v>6923374</v>
+        <v>6923343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,6 +1969,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1990,50 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126242541</v>
+        <v>126242864</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>97227</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604966</v>
+        <v>604927</v>
       </c>
       <c r="R15" t="n">
-        <v>6923343</v>
+        <v>6923374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2071,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126243913</v>
+        <v>126244314</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604846</v>
+        <v>604829</v>
       </c>
       <c r="R5" t="n">
-        <v>6923320</v>
+        <v>6923326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126244314</v>
+        <v>126243913</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91242</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604829</v>
+        <v>604846</v>
       </c>
       <c r="R6" t="n">
-        <v>6923326</v>
+        <v>6923320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126242980</v>
+        <v>126243134</v>
       </c>
       <c r="B7" t="n">
-        <v>91207</v>
+        <v>91538</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604937</v>
+        <v>604973</v>
       </c>
       <c r="R7" t="n">
-        <v>6923369</v>
+        <v>6923382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243134</v>
+        <v>126242980</v>
       </c>
       <c r="B8" t="n">
-        <v>91538</v>
+        <v>91207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604973</v>
+        <v>604937</v>
       </c>
       <c r="R8" t="n">
-        <v>6923382</v>
+        <v>6923369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126244102</v>
+        <v>126241081</v>
       </c>
       <c r="B9" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,21 +1399,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1423,10 +1423,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604829</v>
+        <v>604931</v>
       </c>
       <c r="R9" t="n">
-        <v>6923326</v>
+        <v>6923243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126242691</v>
+        <v>126244102</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,39 +1496,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604953</v>
+        <v>604829</v>
       </c>
       <c r="R10" t="n">
-        <v>6923370</v>
+        <v>6923326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,11 +1556,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126241081</v>
+        <v>126242691</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,34 +1593,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604931</v>
+        <v>604953</v>
       </c>
       <c r="R11" t="n">
-        <v>6923243</v>
+        <v>6923370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1799,7 +1799,7 @@
         <v>126244493</v>
       </c>
       <c r="B13" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>126242864</v>
       </c>
       <c r="B15" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2592,32 +2592,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126242839</v>
+        <v>126242587</v>
       </c>
       <c r="B21" t="n">
-        <v>91696</v>
+        <v>91242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>604916</v>
+        <v>604966</v>
       </c>
       <c r="R21" t="n">
-        <v>6923365</v>
+        <v>6923343</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2689,32 +2689,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126242587</v>
+        <v>126242839</v>
       </c>
       <c r="B22" t="n">
-        <v>91242</v>
+        <v>91696</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>604966</v>
+        <v>604916</v>
       </c>
       <c r="R22" t="n">
-        <v>6923343</v>
+        <v>6923365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2786,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126241476</v>
+        <v>126241499</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>57816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,34 +2797,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604946</v>
+        <v>604927</v>
       </c>
       <c r="R23" t="n">
-        <v>6923307</v>
+        <v>6923303</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,10 +2892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126241499</v>
+        <v>126241476</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>91242</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2894,43 +2903,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604927</v>
+        <v>604946</v>
       </c>
       <c r="R24" t="n">
-        <v>6923303</v>
+        <v>6923307</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -1893,50 +1893,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126242541</v>
+        <v>126242864</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604966</v>
+        <v>604927</v>
       </c>
       <c r="R14" t="n">
-        <v>6923343</v>
+        <v>6923374</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,11 +1964,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2000,45 +1990,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126242864</v>
+        <v>126242541</v>
       </c>
       <c r="B15" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604927</v>
+        <v>604966</v>
       </c>
       <c r="R15" t="n">
-        <v>6923374</v>
+        <v>6923343</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,6 +2066,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126241499</v>
+        <v>126241476</v>
       </c>
       <c r="B23" t="n">
-        <v>57816</v>
+        <v>91242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,43 +2797,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604927</v>
+        <v>604946</v>
       </c>
       <c r="R23" t="n">
-        <v>6923303</v>
+        <v>6923307</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,10 +2883,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126241476</v>
+        <v>126241499</v>
       </c>
       <c r="B24" t="n">
-        <v>91242</v>
+        <v>57816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2903,34 +2894,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604946</v>
+        <v>604927</v>
       </c>
       <c r="R24" t="n">
-        <v>6923307</v>
+        <v>6923303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>56851</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,10 +810,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R3" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +893,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B4" t="n">
-        <v>56851</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,14 +921,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R4" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,32 +1000,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126244314</v>
+        <v>126243913</v>
       </c>
       <c r="B5" t="n">
-        <v>91696</v>
+        <v>91242</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604829</v>
+        <v>604846</v>
       </c>
       <c r="R5" t="n">
-        <v>6923326</v>
+        <v>6923320</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,32 +1097,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126243913</v>
+        <v>126244314</v>
       </c>
       <c r="B6" t="n">
-        <v>91242</v>
+        <v>91696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604846</v>
+        <v>604829</v>
       </c>
       <c r="R6" t="n">
-        <v>6923320</v>
+        <v>6923326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126241081</v>
+        <v>126242691</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>57656</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,34 +1399,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604931</v>
+        <v>604953</v>
       </c>
       <c r="R9" t="n">
-        <v>6923243</v>
+        <v>6923370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1464,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244102</v>
+        <v>126241081</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91242</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604829</v>
+        <v>604931</v>
       </c>
       <c r="R10" t="n">
-        <v>6923326</v>
+        <v>6923243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126242691</v>
+        <v>126244102</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>91538</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,39 +1603,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604953</v>
+        <v>604829</v>
       </c>
       <c r="R11" t="n">
-        <v>6923370</v>
+        <v>6923326</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1893,45 +1893,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126242864</v>
+        <v>126242541</v>
       </c>
       <c r="B14" t="n">
-        <v>97230</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604927</v>
+        <v>604966</v>
       </c>
       <c r="R14" t="n">
-        <v>6923374</v>
+        <v>6923343</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,6 +1969,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1990,50 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126242541</v>
+        <v>126242864</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>97230</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604966</v>
+        <v>604927</v>
       </c>
       <c r="R15" t="n">
-        <v>6923343</v>
+        <v>6923374</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,11 +2071,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B3" t="n">
-        <v>56851</v>
+        <v>57656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,14 +810,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R3" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>56851</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,10 +917,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R4" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126244910</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B3" t="n">
-        <v>57656</v>
+        <v>56852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,10 +810,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R3" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,27 +893,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B4" t="n">
-        <v>56851</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -917,14 +921,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R4" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +1003,7 @@
         <v>126243913</v>
       </c>
       <c r="B5" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>126244314</v>
       </c>
       <c r="B6" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126243134</v>
+        <v>126242980</v>
       </c>
       <c r="B7" t="n">
-        <v>91538</v>
+        <v>91210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604973</v>
+        <v>604937</v>
       </c>
       <c r="R7" t="n">
-        <v>6923382</v>
+        <v>6923369</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126242980</v>
+        <v>126243134</v>
       </c>
       <c r="B8" t="n">
-        <v>91207</v>
+        <v>91541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604937</v>
+        <v>604973</v>
       </c>
       <c r="R8" t="n">
-        <v>6923369</v>
+        <v>6923382</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242691</v>
+        <v>126244102</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>91541</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,39 +1399,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604953</v>
+        <v>604829</v>
       </c>
       <c r="R9" t="n">
-        <v>6923370</v>
+        <v>6923326</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1498,7 +1488,7 @@
         <v>126241081</v>
       </c>
       <c r="B10" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126244102</v>
+        <v>126242691</v>
       </c>
       <c r="B11" t="n">
-        <v>91538</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,34 +1593,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604829</v>
+        <v>604953</v>
       </c>
       <c r="R11" t="n">
-        <v>6923326</v>
+        <v>6923370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1692,7 +1692,7 @@
         <v>126244721</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>126244493</v>
       </c>
       <c r="B13" t="n">
-        <v>100534</v>
+        <v>100543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>126242541</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>126242864</v>
       </c>
       <c r="B15" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>126243475</v>
       </c>
       <c r="B16" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>126243781</v>
       </c>
       <c r="B17" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>126241171</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>126242290</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>126241533</v>
       </c>
       <c r="B20" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>126242587</v>
       </c>
       <c r="B21" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>126242839</v>
       </c>
       <c r="B22" t="n">
-        <v>91696</v>
+        <v>91699</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>126241476</v>
       </c>
       <c r="B23" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         <v>126241499</v>
       </c>
       <c r="B24" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>126244626</v>
       </c>
       <c r="B25" t="n">
-        <v>58025</v>
+        <v>58027</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>126242636</v>
       </c>
       <c r="B26" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -1194,32 +1194,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126242980</v>
+        <v>126243134</v>
       </c>
       <c r="B7" t="n">
-        <v>91210</v>
+        <v>91541</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604937</v>
+        <v>604973</v>
       </c>
       <c r="R7" t="n">
-        <v>6923369</v>
+        <v>6923382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,32 +1291,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126243134</v>
+        <v>126242980</v>
       </c>
       <c r="B8" t="n">
-        <v>91541</v>
+        <v>91210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604973</v>
+        <v>604937</v>
       </c>
       <c r="R8" t="n">
-        <v>6923382</v>
+        <v>6923369</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126244102</v>
+        <v>126242691</v>
       </c>
       <c r="B9" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,34 +1399,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604829</v>
+        <v>604953</v>
       </c>
       <c r="R9" t="n">
-        <v>6923326</v>
+        <v>6923370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1464,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126241081</v>
+        <v>126244102</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604931</v>
+        <v>604829</v>
       </c>
       <c r="R10" t="n">
-        <v>6923243</v>
+        <v>6923326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126242691</v>
+        <v>126241081</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,39 +1603,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604953</v>
+        <v>604931</v>
       </c>
       <c r="R11" t="n">
-        <v>6923370</v>
+        <v>6923243</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126241476</v>
+        <v>126241499</v>
       </c>
       <c r="B23" t="n">
-        <v>91245</v>
+        <v>57817</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,34 +2797,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604946</v>
+        <v>604927</v>
       </c>
       <c r="R23" t="n">
-        <v>6923307</v>
+        <v>6923303</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,10 +2892,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126241499</v>
+        <v>126241476</v>
       </c>
       <c r="B24" t="n">
-        <v>57817</v>
+        <v>91245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2894,43 +2903,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604927</v>
+        <v>604946</v>
       </c>
       <c r="R24" t="n">
-        <v>6923303</v>
+        <v>6923307</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -782,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126244573</v>
+        <v>126244779</v>
       </c>
       <c r="B3" t="n">
-        <v>56852</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -810,14 +810,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604843</v>
+        <v>604898</v>
       </c>
       <c r="R3" t="n">
-        <v>6923281</v>
+        <v>6923266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>En vuxen och en unge</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,27 +889,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126244779</v>
+        <v>126244573</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>56852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,10 +917,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604898</v>
+        <v>604843</v>
       </c>
       <c r="R4" t="n">
-        <v>6923266</v>
+        <v>6923281</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,7 +973,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>En vuxen och en unge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242691</v>
+        <v>126241081</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,39 +1399,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604953</v>
+        <v>604931</v>
       </c>
       <c r="R9" t="n">
-        <v>6923370</v>
+        <v>6923243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126241081</v>
+        <v>126242691</v>
       </c>
       <c r="B11" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,34 +1593,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604931</v>
+        <v>604953</v>
       </c>
       <c r="R11" t="n">
-        <v>6923243</v>
+        <v>6923370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2786,10 +2786,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126241499</v>
+        <v>126241476</v>
       </c>
       <c r="B23" t="n">
-        <v>57817</v>
+        <v>91245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,43 +2797,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>604927</v>
+        <v>604946</v>
       </c>
       <c r="R23" t="n">
-        <v>6923303</v>
+        <v>6923307</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2892,10 +2883,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126241476</v>
+        <v>126241499</v>
       </c>
       <c r="B24" t="n">
-        <v>91245</v>
+        <v>57817</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2903,34 +2894,43 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>604946</v>
+        <v>604927</v>
       </c>
       <c r="R24" t="n">
-        <v>6923307</v>
+        <v>6923303</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126241081</v>
+        <v>126242691</v>
       </c>
       <c r="B9" t="n">
-        <v>91245</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,34 +1399,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604931</v>
+        <v>604953</v>
       </c>
       <c r="R9" t="n">
-        <v>6923243</v>
+        <v>6923370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,6 +1464,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,10 +1495,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126244102</v>
+        <v>126241081</v>
       </c>
       <c r="B10" t="n">
-        <v>91541</v>
+        <v>91245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,21 +1506,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1520,10 +1530,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604829</v>
+        <v>604931</v>
       </c>
       <c r="R10" t="n">
-        <v>6923326</v>
+        <v>6923243</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,10 +1592,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126242691</v>
+        <v>126244102</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>91541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,39 +1603,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604953</v>
+        <v>604829</v>
       </c>
       <c r="R11" t="n">
-        <v>6923370</v>
+        <v>6923326</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1658,11 +1663,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 24498-2025 artfynd.xlsx
+++ b/artfynd/A 24498-2025 artfynd.xlsx
@@ -1388,10 +1388,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126242691</v>
+        <v>126241081</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>91245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1399,39 +1399,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>604953</v>
+        <v>604931</v>
       </c>
       <c r="R9" t="n">
-        <v>6923370</v>
+        <v>6923243</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1464,11 +1459,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-06-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,10 +1485,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126241081</v>
+        <v>126244102</v>
       </c>
       <c r="B10" t="n">
-        <v>91245</v>
+        <v>91541</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,21 +1496,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1530,10 +1520,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>604931</v>
+        <v>604829</v>
       </c>
       <c r="R10" t="n">
-        <v>6923243</v>
+        <v>6923326</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,10 +1582,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126244102</v>
+        <v>126242691</v>
       </c>
       <c r="B11" t="n">
-        <v>91541</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,34 +1593,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Skarpåsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>604829</v>
+        <v>604953</v>
       </c>
       <c r="R11" t="n">
-        <v>6923326</v>
+        <v>6923370</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,6 +1658,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-06-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
